--- a/FreeLayout/Textfile/DispositionProperty.xlsx
+++ b/FreeLayout/Textfile/DispositionProperty.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>Disposition Property List (FA)</t>
   </si>
@@ -195,13 +195,27 @@
     <t>STTHang</t>
   </si>
   <si>
+    <t xml:space="preserve">1CZ849002Z,
+3CQ83311MM
+</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>1RE2DVLB1609ZB</t>
-  </si>
-  <si>
-    <t>ABE</t>
+    <t>8224V</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>102549450840</t>
+  </si>
+  <si>
+    <t>RAM broken</t>
   </si>
   <si>
     <t>1</t>
@@ -264,10 +278,7 @@
     <t>SET</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>1RE1DVLB2059ZA</t>
+    <t>1CZ848033F</t>
   </si>
   <si>
     <t>MY47001020</t>
@@ -291,10 +302,7 @@
     <t>Bộ đếm tần số đo, kiểm tra lượng điện, Model: 53131A, điện áp đầu vào: 100V.</t>
   </si>
   <si>
-    <t>1RE2DVLB1855YB</t>
-  </si>
-  <si>
-    <t>PSNM</t>
+    <t>1CZ849003C</t>
   </si>
   <si>
     <t>53132A</t>
@@ -327,13 +335,10 @@
     <t>PCE</t>
   </si>
   <si>
-    <t>PULB1062ZB-GL</t>
-  </si>
-  <si>
-    <t>SALOM</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1CZ848032P</t>
+  </si>
+  <si>
+    <t>No power up</t>
   </si>
   <si>
     <t>MY40006851</t>
@@ -348,6 +353,15 @@
     <t>BLLDD số 2024.04.19 FADECT-PEDECT</t>
   </si>
   <si>
+    <t>SGH816QZPY</t>
+  </si>
+  <si>
+    <t>8259V</t>
+  </si>
+  <si>
+    <t>102064761520</t>
+  </si>
+  <si>
     <t>High Voltage Digital Voltmeter</t>
   </si>
   <si>
@@ -375,10 +389,144 @@
     <t>JAPAN</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>DVMJ1069ZAK/X1</t>
+    <t>1CZ9010184</t>
+  </si>
+  <si>
+    <t>102533957300</t>
+  </si>
+  <si>
+    <t>SGH821T5VV</t>
+  </si>
+  <si>
+    <t>102168233530</t>
+  </si>
+  <si>
+    <t>CFLTWX1</t>
+  </si>
+  <si>
+    <t>80FP1</t>
+  </si>
+  <si>
+    <t>3757</t>
+  </si>
+  <si>
+    <t>DFPB4Y1</t>
+  </si>
+  <si>
+    <t>70JC4Y1</t>
+  </si>
+  <si>
+    <t>JCX3F2S</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>2DX3F2S</t>
+  </si>
+  <si>
+    <t>5CG8377Q83</t>
+  </si>
+  <si>
+    <t>102283472430</t>
+  </si>
+  <si>
+    <t>5CG8377QMN</t>
+  </si>
+  <si>
+    <t>5CG8195N4Y</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>102104209760</t>
+  </si>
+  <si>
+    <t>5CG8195N8X</t>
+  </si>
+  <si>
+    <t>5CG8195N3H</t>
+  </si>
+  <si>
+    <t>5CD1088S92</t>
+  </si>
+  <si>
+    <t>8301V</t>
+  </si>
+  <si>
+    <t>104048324330</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>EOL, Setup in HP 340S G7 (5CD1088S920</t>
+  </si>
+  <si>
+    <t>R52M502BEYM</t>
+  </si>
+  <si>
+    <t>102728430230</t>
+  </si>
+  <si>
+    <t>5CD0265HF9</t>
+  </si>
+  <si>
+    <t>21HI1</t>
+  </si>
+  <si>
+    <t>103477025150</t>
+  </si>
+  <si>
+    <t>7EKMA73160</t>
+  </si>
+  <si>
+    <t>10PV1</t>
+  </si>
+  <si>
+    <t>101653501940</t>
+  </si>
+  <si>
+    <t>No power up_ PE return</t>
+  </si>
+  <si>
+    <t>R52J30Y2WLB</t>
+  </si>
+  <si>
+    <t>101757638730</t>
+  </si>
+  <si>
+    <t>Screen broken</t>
+  </si>
+  <si>
+    <t>8277V</t>
+  </si>
+  <si>
+    <t>103170483840</t>
+  </si>
+  <si>
+    <t>Broken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F78BR42,
+CN0147F67426173B2NCUA01
+</t>
+  </si>
+  <si>
+    <t>8203V</t>
+  </si>
+  <si>
+    <t>100335810300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC  Mainboard  broken</t>
+  </si>
+  <si>
+    <t>3CQ7321B28</t>
+  </si>
+  <si>
+    <t>101998782060</t>
   </si>
   <si>
     <t>Total</t>
@@ -1440,7 +1588,7 @@
       </c>
       <c r="S4" s="34"/>
       <c r="T4" s="35">
-        <v>45986</v>
+        <v>46181</v>
       </c>
       <c r="U4" s="35"/>
     </row>
@@ -1615,44 +1763,62 @@
         <v>51</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6" s="55">
         <v>1</v>
       </c>
       <c r="H6" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="57" t="s">
-        <v>52</v>
-      </c>
       <c r="J6" s="52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" s="58">
-        <v>43.10541</v>
-      </c>
-      <c r="L6" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="58">
+        <v>0</v>
+      </c>
+      <c r="M6" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S6" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T6" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U6" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V6" s="64">
         <f ref="V6:V10" t="shared" si="0">IF(BA6="USD",AY6,IF(BA6="VND",AY6*0.00004,AY6*0.00714))</f>
         <v>1529.04</v>
@@ -1662,85 +1828,85 @@
         <v>244NDT11Bộ đếm tần số đo, kiểm tra lượng điện 53131A, gồm phụ kiện đi kèm: giấy chứng nhận hiệu chuẩn và sơ đồ dẫn chuẩn.102</v>
       </c>
       <c r="X6" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Y6" s="67" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z6" s="68">
         <v>41730</v>
       </c>
       <c r="AA6" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AB6" s="67" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="AC6" s="67" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD6" s="67" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AE6" s="67">
         <v>1003012061</v>
       </c>
       <c r="AF6" s="67" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AG6" s="67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH6" s="67" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AI6" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ6" s="67" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK6" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AL6" s="69">
         <v>244</v>
       </c>
       <c r="AM6" s="67" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AN6" s="68">
         <v>41727</v>
       </c>
       <c r="AO6" s="67" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AP6" s="67" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AQ6" s="67" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AR6" s="67" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AS6" s="67">
         <v>0</v>
       </c>
       <c r="AT6" s="67" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AU6" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AV6" s="65" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AW6" s="70">
         <v>10</v>
       </c>
       <c r="AX6" s="67" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AY6" s="67">
         <v>1529.04</v>
@@ -1749,7 +1915,7 @@
         <v>15290.4</v>
       </c>
       <c r="BA6" s="67" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BB6" s="67">
         <v>90308990</v>
@@ -1763,47 +1929,65 @@
         <v>2</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7" s="55">
         <v>1</v>
       </c>
       <c r="H7" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I7" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J7" s="52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="58">
-        <v>7.70878</v>
-      </c>
-      <c r="L7" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="62"/>
-      <c r="U7" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="58">
+        <v>0</v>
+      </c>
+      <c r="M7" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="R7" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S7" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T7" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U7" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V7" s="64">
         <f t="shared" si="0"/>
         <v>4470</v>
@@ -1813,76 +1997,76 @@
         <v>630NTA12Bộ đếm tần số đo, kiểm tra lượng điện, Model: 53131A, điện áp đầu vào: 100V.12</v>
       </c>
       <c r="X7" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Y7" s="67" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z7" s="68">
         <v>39512</v>
       </c>
       <c r="AA7" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AB7" s="67" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="AC7" s="67" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD7" s="67" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AE7" s="67">
         <v>1003002074</v>
       </c>
       <c r="AF7" s="67" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AG7" s="67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH7" s="67" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AI7" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ7" s="67" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK7" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AL7" s="69">
         <v>630</v>
       </c>
       <c r="AM7" s="67" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AN7" s="68">
         <v>39512</v>
       </c>
       <c r="AO7" s="67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AP7" s="67" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AQ7" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AR7" s="67" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AS7" s="67">
         <v>0</v>
       </c>
       <c r="AT7" s="67" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AU7" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AV7" s="65">
         <v>0</v>
@@ -1891,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="AX7" s="67" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AY7" s="67">
         <v>4470</v>
@@ -1900,7 +2084,7 @@
         <v>4470</v>
       </c>
       <c r="BA7" s="67" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BB7" s="67">
         <v>0</v>
@@ -1914,47 +2098,65 @@
         <v>3</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8" s="52">
         <v>1</v>
       </c>
       <c r="H8" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I8" s="52" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="K8" s="58">
-        <v>114.06182</v>
-      </c>
-      <c r="L8" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="59"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="61"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="58">
+        <v>0</v>
+      </c>
+      <c r="M8" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U8" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V8" s="64">
         <f t="shared" si="0"/>
         <v>3440.25</v>
@@ -1964,85 +2166,85 @@
         <v>100078664232E13Máy đo tần số dòng điện 100 VAC - 240 VAC. Hàng mới 100%21</v>
       </c>
       <c r="X8" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Y8" s="67" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z8" s="68">
         <v>41849</v>
       </c>
       <c r="AA8" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AB8" s="67" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC8" s="67" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD8" s="67" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AE8" s="67">
         <v>1003012054</v>
       </c>
       <c r="AF8" s="67" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AG8" s="67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH8" s="67" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AI8" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ8" s="67" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK8" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AL8" s="69">
         <v>100078664232</v>
       </c>
       <c r="AM8" s="67" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AN8" s="68">
         <v>41844</v>
       </c>
       <c r="AO8" s="67" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AP8" s="67" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AQ8" s="67" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AR8" s="67" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS8" s="67">
         <v>0</v>
       </c>
       <c r="AT8" s="67" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AU8" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AV8" s="65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AW8" s="70">
         <v>2</v>
       </c>
       <c r="AX8" s="67" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AY8" s="67">
         <v>3440.25</v>
@@ -2051,7 +2253,7 @@
         <v>6880.5</v>
       </c>
       <c r="BA8" s="67" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BB8" s="67">
         <v>90303390</v>
@@ -2065,47 +2267,65 @@
         <v>4</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" s="52">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H9" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9" s="52" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J9" s="52" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="K9" s="58">
-        <v>8.025</v>
-      </c>
-      <c r="L9" s="58" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="59"/>
-      <c r="N9" s="59"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="61"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="62"/>
-      <c r="U9" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="58">
+        <v>0</v>
+      </c>
+      <c r="M9" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q9" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="R9" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S9" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T9" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U9" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V9" s="64">
         <f t="shared" si="0"/>
         <v>1529.04</v>
@@ -2115,85 +2335,85 @@
         <v>244NDT11Bộ đếm tần số đo, kiểm tra lượng điện 53131A, gồm phụ kiện đi kèm: giấy chứng nhận hiệu chuẩn và sơ đồ dẫn chuẩn.102</v>
       </c>
       <c r="X9" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Y9" s="67" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z9" s="68">
         <v>41730</v>
       </c>
       <c r="AA9" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AB9" s="67" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="AC9" s="67" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD9" s="67" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AE9" s="67">
         <v>1003012067</v>
       </c>
       <c r="AF9" s="67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" s="67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH9" s="67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AI9" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ9" s="67" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK9" s="67" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL9" s="69">
         <v>244</v>
       </c>
       <c r="AM9" s="67" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AN9" s="68">
         <v>41727</v>
       </c>
       <c r="AO9" s="67" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AP9" s="67" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AQ9" s="67" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AR9" s="67" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AS9" s="67">
         <v>0</v>
       </c>
       <c r="AT9" s="67" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AU9" s="67" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AV9" s="65" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AW9" s="70">
         <v>10</v>
       </c>
       <c r="AX9" s="67" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AY9" s="67">
         <v>1529.04</v>
@@ -2202,7 +2422,7 @@
         <v>15290.4</v>
       </c>
       <c r="BA9" s="67" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BB9" s="67">
         <v>90308990</v>
@@ -2216,47 +2436,65 @@
         <v>5</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" s="52">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H10" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K10" s="58">
-        <v>8.025</v>
-      </c>
-      <c r="L10" s="58" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="59"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="58">
+        <v>0</v>
+      </c>
+      <c r="M10" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q10" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="R10" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T10" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U10" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V10" s="64">
         <f t="shared" si="0"/>
         <v>1700</v>
@@ -2266,52 +2504,52 @@
         <v>103229186060E13Thiết bị đo điệp áp cao, điện áp: 100VAC, 50/60Hz, Model: 149-10A, Hãng sản xuất: Kikusui, Hàng mới 100%13</v>
       </c>
       <c r="X10" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Y10" s="67" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z10" s="68">
         <v>43917</v>
       </c>
       <c r="AA10" s="67" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AB10" s="67" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AC10" s="67" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AD10" s="67" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AE10" s="67">
         <v>1003013388</v>
       </c>
       <c r="AF10" s="67" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AG10" s="67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH10" s="67" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AI10" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ10" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AK10" s="67" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AL10" s="69">
         <v>103229186060</v>
       </c>
       <c r="AM10" s="67" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AN10" s="68">
         <v>43918</v>
@@ -2326,25 +2564,25 @@
         <v>112000006873819</v>
       </c>
       <c r="AR10" s="67" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AS10" s="67" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AT10" s="67" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AU10" s="67" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AV10" s="65" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AW10" s="70">
         <v>1</v>
       </c>
       <c r="AX10" s="67" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AY10" s="67">
         <v>1700</v>
@@ -2353,7 +2591,7 @@
         <v>1700</v>
       </c>
       <c r="BA10" s="67" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="BB10" s="67">
         <v>90303390</v>
@@ -2367,47 +2605,65 @@
         <v>6</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" s="52">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H11" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I11" s="52" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K11" s="58">
-        <v>8.025</v>
-      </c>
-      <c r="L11" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="62"/>
-      <c r="U11" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="58">
+        <v>0</v>
+      </c>
+      <c r="M11" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q11" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="R11" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T11" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U11" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V11" s="64"/>
       <c r="W11" s="65"/>
       <c r="X11" s="66"/>
@@ -2448,47 +2704,65 @@
         <v>7</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G12" s="52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I12" s="52" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="K12" s="58">
-        <v>9.9876</v>
-      </c>
-      <c r="L12" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="59"/>
-      <c r="N12" s="59"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="61"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="62"/>
-      <c r="U12" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="58">
+        <v>0</v>
+      </c>
+      <c r="M12" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q12" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="R12" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T12" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U12" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V12" s="64"/>
       <c r="W12" s="65"/>
       <c r="X12" s="66"/>
@@ -2529,47 +2803,65 @@
         <v>8</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G13" s="52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I13" s="52" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="K13" s="58">
-        <v>9.9876</v>
-      </c>
-      <c r="L13" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="59"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="58">
+        <v>0</v>
+      </c>
+      <c r="M13" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q13" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="R13" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T13" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U13" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V13" s="64"/>
       <c r="W13" s="65"/>
       <c r="X13" s="66"/>
@@ -2606,27 +2898,69 @@
       <c r="BC13" s="67"/>
     </row>
     <row r="14" ht="15" s="71" customFormat="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="62"/>
-      <c r="U14" s="63"/>
+      <c r="A14" s="52">
+        <v>9</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="52">
+        <v>1</v>
+      </c>
+      <c r="H14" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="K14" s="58">
+        <v>0</v>
+      </c>
+      <c r="L14" s="58">
+        <v>0</v>
+      </c>
+      <c r="M14" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q14" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="R14" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T14" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U14" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V14" s="64"/>
       <c r="W14" s="65"/>
       <c r="X14" s="66"/>
@@ -2663,27 +2997,69 @@
       <c r="BC14" s="67"/>
     </row>
     <row r="15" ht="15" s="71" customFormat="1">
-      <c r="A15" s="52"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="62"/>
-      <c r="U15" s="63"/>
+      <c r="A15" s="52">
+        <v>10</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="52">
+        <v>1</v>
+      </c>
+      <c r="H15" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="K15" s="58">
+        <v>0</v>
+      </c>
+      <c r="L15" s="58">
+        <v>0</v>
+      </c>
+      <c r="M15" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q15" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T15" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U15" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V15" s="64"/>
       <c r="W15" s="65"/>
       <c r="X15" s="66"/>
@@ -2720,27 +3096,69 @@
       <c r="BC15" s="67"/>
     </row>
     <row r="16" ht="15" s="71" customFormat="1">
-      <c r="A16" s="52"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="62"/>
-      <c r="U16" s="63"/>
+      <c r="A16" s="52">
+        <v>11</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="52">
+        <v>1</v>
+      </c>
+      <c r="H16" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="K16" s="58">
+        <v>0</v>
+      </c>
+      <c r="L16" s="58">
+        <v>0</v>
+      </c>
+      <c r="M16" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q16" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="R16" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S16" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T16" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U16" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V16" s="64"/>
       <c r="W16" s="65"/>
       <c r="X16" s="66"/>
@@ -2777,27 +3195,69 @@
       <c r="BC16" s="67"/>
     </row>
     <row r="17" ht="15" s="71" customFormat="1">
-      <c r="A17" s="52"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="61"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="63"/>
+      <c r="A17" s="52">
+        <v>12</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="52">
+        <v>1</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="K17" s="58">
+        <v>0</v>
+      </c>
+      <c r="L17" s="58">
+        <v>0</v>
+      </c>
+      <c r="M17" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P17" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="R17" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S17" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T17" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="U17" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V17" s="64"/>
       <c r="W17" s="65"/>
       <c r="X17" s="66"/>
@@ -2834,27 +3294,69 @@
       <c r="BC17" s="67"/>
     </row>
     <row r="18" ht="15" s="71" customFormat="1">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="60"/>
-      <c r="T18" s="62"/>
-      <c r="U18" s="63"/>
+      <c r="A18" s="52">
+        <v>13</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="52">
+        <v>1</v>
+      </c>
+      <c r="H18" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="58">
+        <v>0</v>
+      </c>
+      <c r="L18" s="58">
+        <v>0</v>
+      </c>
+      <c r="M18" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q18" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="R18" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S18" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T18" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U18" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V18" s="64"/>
       <c r="W18" s="65"/>
       <c r="X18" s="66"/>
@@ -2891,27 +3393,69 @@
       <c r="BC18" s="67"/>
     </row>
     <row r="19" ht="15" s="71" customFormat="1">
-      <c r="A19" s="52"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="60"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="60"/>
-      <c r="T19" s="62"/>
-      <c r="U19" s="63"/>
+      <c r="A19" s="52">
+        <v>14</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="52">
+        <v>1</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K19" s="58">
+        <v>0</v>
+      </c>
+      <c r="L19" s="58">
+        <v>0</v>
+      </c>
+      <c r="M19" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P19" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q19" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S19" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T19" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U19" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V19" s="64"/>
       <c r="W19" s="65"/>
       <c r="X19" s="66"/>
@@ -2948,27 +3492,69 @@
       <c r="BC19" s="67"/>
     </row>
     <row r="20" ht="15" s="71" customFormat="1">
-      <c r="A20" s="52"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="60"/>
-      <c r="Q20" s="60"/>
-      <c r="R20" s="61"/>
-      <c r="S20" s="60"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="63"/>
+      <c r="A20" s="52">
+        <v>15</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="52">
+        <v>1</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="J20" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K20" s="58">
+        <v>0</v>
+      </c>
+      <c r="L20" s="58">
+        <v>0</v>
+      </c>
+      <c r="M20" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="N20" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P20" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q20" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="R20" s="61">
+        <v>43350</v>
+      </c>
+      <c r="S20" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T20" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U20" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V20" s="64"/>
       <c r="W20" s="65"/>
       <c r="X20" s="66"/>
@@ -3005,27 +3591,69 @@
       <c r="BC20" s="67"/>
     </row>
     <row r="21" ht="15" s="71" customFormat="1">
-      <c r="A21" s="52"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="60"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="63"/>
+      <c r="A21" s="52">
+        <v>16</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="52">
+        <v>1</v>
+      </c>
+      <c r="H21" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="J21" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K21" s="58">
+        <v>0</v>
+      </c>
+      <c r="L21" s="58">
+        <v>0</v>
+      </c>
+      <c r="M21" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="N21" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P21" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q21" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="R21" s="61">
+        <v>43350</v>
+      </c>
+      <c r="S21" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T21" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U21" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V21" s="64"/>
       <c r="W21" s="65"/>
       <c r="X21" s="66"/>
@@ -3062,27 +3690,69 @@
       <c r="BC21" s="67"/>
     </row>
     <row r="22" ht="15" s="71" customFormat="1">
-      <c r="A22" s="52"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="60"/>
-      <c r="T22" s="62"/>
-      <c r="U22" s="63"/>
+      <c r="A22" s="52">
+        <v>17</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="52">
+        <v>1</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K22" s="58">
+        <v>0</v>
+      </c>
+      <c r="L22" s="58">
+        <v>0</v>
+      </c>
+      <c r="M22" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="N22" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P22" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q22" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="R22" s="61">
+        <v>43350</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T22" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U22" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V22" s="64"/>
       <c r="W22" s="65"/>
       <c r="X22" s="66"/>
@@ -3119,27 +3789,69 @@
       <c r="BC22" s="67"/>
     </row>
     <row r="23" ht="15" s="71" customFormat="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="52"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="60"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="63"/>
+      <c r="A23" s="52">
+        <v>18</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="52">
+        <v>1</v>
+      </c>
+      <c r="H23" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="J23" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="K23" s="58">
+        <v>0</v>
+      </c>
+      <c r="L23" s="58">
+        <v>0</v>
+      </c>
+      <c r="M23" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q23" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="R23" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T23" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U23" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V23" s="64"/>
       <c r="W23" s="65"/>
       <c r="X23" s="66"/>
@@ -3176,27 +3888,69 @@
       <c r="BC23" s="67"/>
     </row>
     <row r="24" ht="15" s="71" customFormat="1">
-      <c r="A24" s="52"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="59"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="61"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="63"/>
+      <c r="A24" s="52">
+        <v>19</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="52">
+        <v>1</v>
+      </c>
+      <c r="H24" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="J24" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" s="58">
+        <v>0</v>
+      </c>
+      <c r="L24" s="58">
+        <v>0</v>
+      </c>
+      <c r="M24" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P24" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q24" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="R24" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S24" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T24" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="U24" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V24" s="64"/>
       <c r="W24" s="65"/>
       <c r="X24" s="66"/>
@@ -3233,27 +3987,69 @@
       <c r="BC24" s="67"/>
     </row>
     <row r="25" ht="15" s="71" customFormat="1">
-      <c r="A25" s="52"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="52"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="61"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="62"/>
-      <c r="U25" s="63"/>
+      <c r="A25" s="52">
+        <v>20</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="52">
+        <v>1</v>
+      </c>
+      <c r="H25" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="K25" s="58">
+        <v>0</v>
+      </c>
+      <c r="L25" s="58">
+        <v>0</v>
+      </c>
+      <c r="M25" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q25" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="R25" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S25" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T25" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U25" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V25" s="64"/>
       <c r="W25" s="65"/>
       <c r="X25" s="66"/>
@@ -3290,27 +4086,69 @@
       <c r="BC25" s="67"/>
     </row>
     <row r="26" ht="15" s="71" customFormat="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="61"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="62"/>
-      <c r="U26" s="63"/>
+      <c r="A26" s="52">
+        <v>21</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="52">
+        <v>1</v>
+      </c>
+      <c r="H26" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="K26" s="58">
+        <v>0</v>
+      </c>
+      <c r="L26" s="58">
+        <v>0</v>
+      </c>
+      <c r="M26" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q26" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="R26" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S26" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T26" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="U26" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V26" s="64"/>
       <c r="W26" s="65"/>
       <c r="X26" s="66"/>
@@ -3347,27 +4185,69 @@
       <c r="BC26" s="67"/>
     </row>
     <row r="27" ht="15" s="71" customFormat="1">
-      <c r="A27" s="52"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="61"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="62"/>
-      <c r="U27" s="63"/>
+      <c r="A27" s="52">
+        <v>22</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="52">
+        <v>1</v>
+      </c>
+      <c r="H27" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="J27" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="58">
+        <v>0</v>
+      </c>
+      <c r="L27" s="58">
+        <v>0</v>
+      </c>
+      <c r="M27" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="N27" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O27" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P27" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q27" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="R27" s="61">
+        <v>43079</v>
+      </c>
+      <c r="S27" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T27" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="U27" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V27" s="64"/>
       <c r="W27" s="65"/>
       <c r="X27" s="66"/>
@@ -3404,27 +4284,69 @@
       <c r="BC27" s="67"/>
     </row>
     <row r="28" ht="15" s="71" customFormat="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="61"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="62"/>
-      <c r="U28" s="63"/>
+      <c r="A28" s="52">
+        <v>23</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="52">
+        <v>1</v>
+      </c>
+      <c r="H28" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" s="58">
+        <v>0</v>
+      </c>
+      <c r="L28" s="58">
+        <v>0</v>
+      </c>
+      <c r="M28" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O28" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P28" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q28" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="R28" s="61">
+        <v>43051</v>
+      </c>
+      <c r="S28" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T28" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="U28" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V28" s="64"/>
       <c r="W28" s="65"/>
       <c r="X28" s="66"/>
@@ -3461,27 +4383,69 @@
       <c r="BC28" s="67"/>
     </row>
     <row r="29" ht="15" s="71" customFormat="1">
-      <c r="A29" s="52"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="61"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="62"/>
-      <c r="U29" s="63"/>
+      <c r="A29" s="52">
+        <v>24</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="52">
+        <v>2</v>
+      </c>
+      <c r="H29" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="K29" s="58">
+        <v>0</v>
+      </c>
+      <c r="L29" s="58">
+        <v>0</v>
+      </c>
+      <c r="M29" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N29" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P29" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q29" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="R29" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S29" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T29" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="U29" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V29" s="64"/>
       <c r="W29" s="65"/>
       <c r="X29" s="66"/>
@@ -3518,27 +4482,69 @@
       <c r="BC29" s="67"/>
     </row>
     <row r="30" ht="15" s="71" customFormat="1">
-      <c r="A30" s="52"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="61"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="62"/>
-      <c r="U30" s="63"/>
+      <c r="A30" s="52">
+        <v>25</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="52">
+        <v>1</v>
+      </c>
+      <c r="H30" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="K30" s="58">
+        <v>0</v>
+      </c>
+      <c r="L30" s="58">
+        <v>0</v>
+      </c>
+      <c r="M30" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="N30" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O30" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P30" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q30" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="R30" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="S30" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T30" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="U30" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V30" s="64"/>
       <c r="W30" s="65"/>
       <c r="X30" s="66"/>
@@ -3575,27 +4581,69 @@
       <c r="BC30" s="67"/>
     </row>
     <row r="31" ht="15" s="71" customFormat="1">
-      <c r="A31" s="52"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="60"/>
-      <c r="T31" s="62"/>
-      <c r="U31" s="63"/>
+      <c r="A31" s="52">
+        <v>26</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="52">
+        <v>1</v>
+      </c>
+      <c r="H31" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="J31" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K31" s="58">
+        <v>0</v>
+      </c>
+      <c r="L31" s="58">
+        <v>0</v>
+      </c>
+      <c r="M31" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="P31" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q31" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="61">
+        <v>43378</v>
+      </c>
+      <c r="S31" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="T31" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="U31" s="63" t="s">
+        <v>58</v>
+      </c>
       <c r="V31" s="64"/>
       <c r="W31" s="65"/>
       <c r="X31" s="66"/>
@@ -6084,7 +7132,7 @@
     </row>
     <row r="75" ht="18.75" s="71" customFormat="1">
       <c r="A75" s="85" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="B75" s="86"/>
       <c r="C75" s="86"/>
